--- a/data/trans_orig/ED_INF-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Edad-trans_orig.xlsx
@@ -716,27 +716,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,16</t>
+          <t>0,88; 1,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,82; 1,04</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0,81; 1,03</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,84; 1,04</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,43</t>
+          <t>1,15; 1,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,15</t>
+          <t>0,91; 1,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,32 +746,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,04</t>
+          <t>0,83; 1,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,23</t>
+          <t>0,93; 1,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,11</t>
+          <t>0,92; 1,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 0,98</t>
+          <t>0,83; 0,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,01</t>
+          <t>0,84; 1,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,3</t>
+          <t>1,08; 1,3</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 5,12</t>
+          <t>4,85; 5,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,2</t>
+          <t>4,9; 5,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,21</t>
+          <t>4,93; 5,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 5,5</t>
+          <t>5,17; 5,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,23</t>
+          <t>4,93; 5,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 5,23</t>
+          <t>4,94; 5,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 5,42</t>
+          <t>5,05; 5,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,05</t>
+          <t>4,86; 5,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 5,17</t>
+          <t>4,96; 5,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 5,18</t>
+          <t>4,99; 5,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,71</t>
+          <t>9,4; 9,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,64</t>
+          <t>9,38; 9,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,42 +1016,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 9,65</t>
+          <t>9,38; 9,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,77</t>
+          <t>9,48; 9,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,72</t>
+          <t>9,46; 9,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 9,76</t>
+          <t>9,46; 9,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 9,65</t>
+          <t>9,42; 9,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,53; 9,72</t>
+          <t>9,52; 9,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,65</t>
+          <t>9,47; 9,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 9,66</t>
+          <t>9,47; 9,67</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,45; 13,76</t>
+          <t>13,47; 13,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 13,65</t>
+          <t>13,36; 13,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,17 +1156,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 13,88</t>
+          <t>13,63; 13,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 13,74</t>
+          <t>13,45; 13,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 13,9</t>
+          <t>13,6; 13,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 13,8</t>
+          <t>13,62; 13,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,49; 13,7</t>
+          <t>13,5; 13,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 13,73</t>
+          <t>13,53; 13,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,72; 14,03</t>
+          <t>13,72; 14,04</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,01</t>
+          <t>7,41; 7,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,57</t>
+          <t>6,99; 7,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,86</t>
+          <t>7,29; 7,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,26; 10,26</t>
+          <t>9,22; 10,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,98</t>
+          <t>7,43; 7,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,55</t>
+          <t>6,97; 7,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,84</t>
+          <t>7,29; 7,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,9</t>
+          <t>9,24; 9,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,88</t>
+          <t>7,49; 7,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,09; 7,47</t>
+          <t>7,05; 7,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,76</t>
+          <t>7,36; 7,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,95</t>
+          <t>9,36; 9,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_INF-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,03</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,94</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,09</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,01</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,93</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,93</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,03</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,21</t>
         </is>
       </c>
     </row>
@@ -716,47 +716,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,14</t>
+          <t>0,9; 1,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,04</t>
+          <t>0,78; 1,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,03</t>
+          <t>0,83; 1,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,44</t>
+          <t>0,95; 1,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,17</t>
+          <t>0,89; 1,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 0,99</t>
+          <t>0,82; 1,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,05</t>
+          <t>0,82; 1,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,24</t>
+          <t>1,19; 1,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,11</t>
+          <t>0,93; 1,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,01</t>
+          <t>0,86; 1,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,3</t>
+          <t>1,11; 1,32</t>
         </is>
       </c>
     </row>
@@ -788,62 +788,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,09</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,34</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,06</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,07</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,33</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,93</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5,42</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4,96</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5,07</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>5,08</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,09</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4,96</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>5,38</t>
         </is>
       </c>
     </row>
@@ -856,52 +856,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,13</t>
+          <t>4,78; 5,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,2</t>
+          <t>4,95; 5,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 5,22</t>
+          <t>4,95; 5,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 5,5</t>
+          <t>5,15; 5,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,07</t>
+          <t>4,83; 5,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 5,22</t>
+          <t>4,91; 5,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,22</t>
+          <t>4,93; 5,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 5,44</t>
+          <t>5,25; 5,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,07</t>
+          <t>4,86; 5,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 5,17</t>
+          <t>4,97; 5,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 5,41</t>
+          <t>5,26; 5,51</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,51</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,59</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,61</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,55</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,61</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,51</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,59</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>9,53</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 9,72</t>
+          <t>9,37; 9,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 9,75</t>
+          <t>9,48; 9,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>9,44; 9,71</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9,46; 9,75</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,38; 9,72</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9,48; 9,77</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>9,38; 9,64</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,35; 9,67</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,38; 9,64</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 9,76</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,46; 9,72</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,75</t>
+          <t>9,37; 9,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,64</t>
+          <t>9,43; 9,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,52; 9,72</t>
+          <t>9,53; 9,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 9,64</t>
+          <t>9,46; 9,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 9,67</t>
+          <t>9,47; 9,68</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13,75</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,59</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,75</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13,79</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,61</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13,51</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,87</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,75</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,59</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,75</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,81</t>
+          <t>13,77</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>13,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 13,81</t>
+          <t>13,62; 13,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,47; 13,77</t>
+          <t>13,46; 13,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,36; 13,65</t>
+          <t>13,62; 13,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,69; 14,19</t>
+          <t>13,66; 13,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 13,88</t>
+          <t>13,57; 13,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,45; 13,74</t>
+          <t>13,46; 13,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 13,89</t>
+          <t>13,37; 13,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 13,98</t>
+          <t>13,64; 13,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 13,81</t>
+          <t>13,62; 13,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 13,7</t>
+          <t>13,5; 13,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 13,74</t>
+          <t>13,52; 13,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,72; 14,04</t>
+          <t>13,68; 13,89</t>
         </is>
       </c>
     </row>
@@ -1208,62 +1208,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,69</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,26</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,56</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,78</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,27</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>7,69</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>7,26</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9,56</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,71</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,97</t>
+          <t>7,39; 7,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,57</t>
+          <t>6,97; 7,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,84</t>
+          <t>7,3; 7,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 10,25</t>
+          <t>9,48; 10,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,99</t>
+          <t>7,44; 8,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,54</t>
+          <t>6,96; 7,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,83</t>
+          <t>7,27; 7,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,91</t>
+          <t>9,34; 9,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,91</t>
+          <t>7,48; 7,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,44</t>
+          <t>7,06; 7,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,77</t>
+          <t>7,35; 7,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,36; 9,96</t>
+          <t>9,52; 9,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_INF-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,03</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.032822559103237</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8844177421619933</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9365281509645518</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.093135540421344</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.013965637006211</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.9271847157573303</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.9320762716202794</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1.331906792241611</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1.024024259748088</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0.9058575410296615</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0.9342370327009978</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>1.214326678143865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,9; 1,16</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,78; 1,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,83; 1,05</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,95; 1,25</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,89; 1,16</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 1,03</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 1,03</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 1,46</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,93; 1,11</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,83; 0,98</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0,86; 1,01</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,11; 1,32</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8990137853343315</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.7763118970871093</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8276326529354762</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.9461980963678444</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.8853224554260513</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.8231242857981945</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.8200098818724465</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.193290986252948</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.9305313396143445</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.8260412262466084</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.8567566827837851</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>1.108817995612339</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.158413733104438</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9962392361661986</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.050947788789877</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.247032245705924</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.155778543181868</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.030944782907629</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1.032769390626908</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1.461301435266116</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>1.111472590267518</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0.9833086143736751</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1.011637518478339</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>1.318218607002073</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,93</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,09</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,98</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,42</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4,96</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,78; 5,07</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,95; 5,24</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,95; 5,22</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5,15; 5,52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,83; 5,12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,91; 5,21</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,93; 5,23</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5,25; 5,59</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4,86; 5,05</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4,97; 5,18</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4,99; 5,18</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,26; 5,51</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.930457958440339</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.080834263887827</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.086319263266545</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5.343352105218663</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>4.982104267311029</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>5.060852868356469</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.071711323972102</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>5.417181388863488</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>4.956253037794648</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>5.07149099007608</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>5.079756381897021</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>5.37880450643175</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,59</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,61</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>9,57</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4.778056631968873</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4.94884704344557</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>4.950422527276337</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>5.149338897624674</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>4.832573823586896</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>4.908752177063998</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>4.931811617805814</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>5.248953608593968</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>4.863315982246212</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>4.969385492999154</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>4.985711660752449</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>5.262069736160311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>9,37; 9,64</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 9,76</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,44; 9,71</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,46; 9,75</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,38; 9,72</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 9,77</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,38; 9,64</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,37; 9,68</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>9,43; 9,63</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9,53; 9,72</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9,46; 9,65</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,47; 9,68</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.074359581709721</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.237197054313521</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.224256076079483</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.524715916629344</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5.116842168332548</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>5.210324288803688</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.228646314881189</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>5.592813384272818</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5.050980066843965</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>5.17518475864134</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>5.179889628281813</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>5.511250973942656</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13,75</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13,59</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,75</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,79</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,61</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,51</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13,77</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13,72</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13,6</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13,63</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,78</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>9.511026560640056</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9.629066733810511</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.591562722139884</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>9.606133061622288</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>9.547121320704818</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>9.613847892419116</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>9.513389768721165</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>9.533749386964907</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9.528137093761313</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>9.621494147104059</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>9.552442384636928</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>9.572312100010326</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>13,62; 13,87</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13,46; 13,73</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13,62; 13,9</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13,66; 13,95</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13,57; 13,82</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,46; 13,76</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13,37; 13,65</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13,64; 13,91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13,62; 13,79</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13,5; 13,71</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>13,52; 13,73</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>13,68; 13,89</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>9.373719130520229</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>9.475141858768946</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>9.442502306451622</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>9.462157745477652</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>9.37731104027714</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>9.478116885669275</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>9.380091953763507</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>9.365505265929146</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>9.430128467545018</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>9.525495818557845</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>9.460943814297975</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>9.471043069467376</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.644346155574496</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>9.757417867858505</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.714789913857565</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.749480000077225</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>9.717053332591039</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>9.768271713049039</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>9.638739609376229</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9.678050054635198</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>9.628817656562974</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>9.722247486511758</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>9.651556891764137</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>9.676816871265515</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>13.74715111793594</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>13.59217384234392</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>13.7549631070449</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>13.78829186150033</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>13.68120454545556</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>13.60833863921942</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>13.50756447877554</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>13.77100378264462</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>13.71516271740213</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>13.60005795546048</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>13.63152983096552</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>13.78021587743818</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>13.62331749154989</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>13.46308001694195</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>13.61503400757104</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>13.65774276660024</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>13.5738066480709</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>13.4590027696457</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>13.36524231305117</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>13.64451482508558</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>13.61733382550928</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>13.49833081592272</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>13.52175483622965</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>13.68322978347733</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>13.87131104912504</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>13.72674100076324</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>13.89674272048797</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>13.94766035340753</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>13.81826458578183</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>13.76485393582536</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>13.6518574054485</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>13.90618154032433</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>13.79496227704045</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>13.70524055721192</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>13.73406778546952</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>13.88741045527058</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,78</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,7</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,27</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7,39; 7,99</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6,97; 7,54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7,3; 7,85</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 10,1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,44; 8,0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,96; 7,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,27; 7,87</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9,34; 9,91</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7,48; 7,9</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7,06; 7,45</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7,35; 7,76</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,52; 9,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>7.686503722220882</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7.257644538882922</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>7.560752428861319</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>9.780471477728199</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>7.697767415738436</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>7.271810580812661</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>7.564667708404688</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>9.630335428656423</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7.691968349363568</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>7.264523921937828</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>7.562655396620261</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>9.709417831196458</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>7.388847330498332</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>6.967653759609462</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>7.296124518993391</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>9.475469669784273</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>7.435603977477592</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>6.960188731507415</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>7.267688705319162</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>9.338891050971011</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>7.483051501231841</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>7.055665257880269</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>7.347803524329539</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>9.517593386670626</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.987741645299486</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.54324902018594</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.850289141082586</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>10.09525800757605</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>8.002345327215043</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>7.554722198807807</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>7.872403767905337</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>9.911925337327148</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7.900606896418965</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>7.452135021602592</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>7.761344036894315</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>9.934697345666024</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
